--- a/data/trans_dic/P35-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P35-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 21,47</t>
+          <t>14,25; 21,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 31,28</t>
+          <t>21,98; 31,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,24; 36,01</t>
+          <t>25,76; 35,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,26; 38,57</t>
+          <t>29,83; 38,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 21,46</t>
+          <t>12,76; 21,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 34,27</t>
+          <t>22,91; 33,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 34,21</t>
+          <t>24,72; 34,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,37; 31,44</t>
+          <t>24,83; 31,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 20,54</t>
+          <t>14,45; 19,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,91; 30,83</t>
+          <t>23,68; 30,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,5; 33,53</t>
+          <t>26,52; 33,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,55; 34,17</t>
+          <t>28,35; 34,01</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 24,29</t>
+          <t>15,41; 24,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,1; 31,57</t>
+          <t>21,39; 31,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 32,76</t>
+          <t>23,49; 32,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,04; 43,52</t>
+          <t>33,93; 43,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 19,38</t>
+          <t>10,97; 19,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,96; 36,21</t>
+          <t>25,01; 35,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 36,17</t>
+          <t>25,97; 35,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,7; 41,98</t>
+          <t>33,07; 41,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,45</t>
+          <t>14,43; 20,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,53; 31,92</t>
+          <t>24,46; 31,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 32,93</t>
+          <t>25,68; 32,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,94; 41,06</t>
+          <t>35,29; 41,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 24,15</t>
+          <t>17,2; 24,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 33,15</t>
+          <t>25,2; 32,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,16; 36,68</t>
+          <t>27,56; 36,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 40,28</t>
+          <t>9,17; 40,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 28,31</t>
+          <t>14,95; 27,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,14; 42,33</t>
+          <t>30,02; 42,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,72; 44,28</t>
+          <t>29,02; 44,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,59; 48,04</t>
+          <t>35,38; 48,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 23,79</t>
+          <t>17,66; 23,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,96; 34,06</t>
+          <t>27,8; 34,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,63; 36,93</t>
+          <t>29,44; 36,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 40,76</t>
+          <t>13,73; 40,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,48</t>
+          <t>17,82; 22,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,13; 31,61</t>
+          <t>26,14; 31,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 31,39</t>
+          <t>26,11; 31,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 39,35</t>
+          <t>32,57; 39,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,07</t>
+          <t>17,08; 23,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 34,92</t>
+          <t>27,87; 35,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,44; 35,32</t>
+          <t>28,49; 34,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 33,63</t>
+          <t>12,18; 33,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 21,88</t>
+          <t>18,31; 21,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,55; 32,18</t>
+          <t>27,76; 32,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 32,31</t>
+          <t>27,9; 32,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 35,19</t>
+          <t>21,76; 35,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 15,57</t>
+          <t>8,35; 15,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,09; 30,01</t>
+          <t>21,69; 30,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 32,2</t>
+          <t>25,07; 32,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,58; 36,79</t>
+          <t>28,18; 36,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,83</t>
+          <t>14,31; 21,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,0; 37,49</t>
+          <t>30,12; 37,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,7; 46,31</t>
+          <t>38,46; 46,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,57; 45,87</t>
+          <t>30,68; 46,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,87; 17,78</t>
+          <t>12,9; 17,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,94; 33,32</t>
+          <t>27,82; 33,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,32; 38,95</t>
+          <t>33,09; 38,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,81; 40,94</t>
+          <t>30,04; 40,98</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,78</t>
+          <t>3,53; 9,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,41</t>
+          <t>3,34; 9,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 14,86</t>
+          <t>6,8; 14,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,55; 26,01</t>
+          <t>11,09; 26,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,62; 30,04</t>
+          <t>25,04; 30,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,15; 42,36</t>
+          <t>36,24; 42,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,21; 38,08</t>
+          <t>32,07; 38,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,09; 44,87</t>
+          <t>38,14; 44,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 25,52</t>
+          <t>21,32; 25,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,29; 35,52</t>
+          <t>30,21; 35,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,5; 32,81</t>
+          <t>27,36; 32,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,66; 38,87</t>
+          <t>32,31; 38,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,16; 18,82</t>
+          <t>16,39; 19,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,32; 27,62</t>
+          <t>24,42; 27,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,33; 29,45</t>
+          <t>26,32; 29,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,19; 34,93</t>
+          <t>24,93; 34,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,21; 23,15</t>
+          <t>20,14; 23,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,6; 36,0</t>
+          <t>32,81; 36,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,2; 36,62</t>
+          <t>33,13; 36,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,12; 38,0</t>
+          <t>28,45; 37,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 20,74</t>
+          <t>18,64; 20,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,13; 31,42</t>
+          <t>29,12; 31,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,3; 32,71</t>
+          <t>30,16; 32,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 35,77</t>
+          <t>29,07; 35,85</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65978; 97684</t>
+          <t>64823; 97753</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93285; 133708</t>
+          <t>93943; 133323</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111113; 152510</t>
+          <t>109100; 148937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152856; 194864</t>
+          <t>150701; 194761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36562; 63124</t>
+          <t>37546; 62547</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70875; 104310</t>
+          <t>69734; 101646</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83340; 117693</t>
+          <t>85031; 118489</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>109069; 140673</t>
+          <t>111115; 140402</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109228; 153841</t>
+          <t>108272; 148872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174983; 225608</t>
+          <t>173290; 225131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203370; 257332</t>
+          <t>203538; 256355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>272003; 325483</t>
+          <t>270124; 324051</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54731; 84484</t>
+          <t>53594; 84424</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89202; 127435</t>
+          <t>86333; 127088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85221; 120801</t>
+          <t>86598; 120230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153948; 196782</t>
+          <t>153453; 194822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39711; 66583</t>
+          <t>37674; 66553</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82160; 119180</t>
+          <t>82308; 118420</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95121; 132384</t>
+          <t>95063; 131531</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128650; 160259</t>
+          <t>126255; 159179</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99934; 141398</t>
+          <t>99785; 138902</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179737; 233873</t>
+          <t>179205; 233150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191789; 241931</t>
+          <t>188638; 241427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>291356; 342435</t>
+          <t>294288; 346434</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>87438; 124596</t>
+          <t>88739; 125322</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153848; 201203</t>
+          <t>152903; 199217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144640; 188425</t>
+          <t>141552; 185900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61597; 269162</t>
+          <t>61303; 269612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24414; 45800</t>
+          <t>24194; 45267</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77149; 108356</t>
+          <t>76836; 108199</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47136; 72675</t>
+          <t>47623; 72933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59403; 80185</t>
+          <t>59050; 80147</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120772; 161198</t>
+          <t>119667; 160178</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241224; 293888</t>
+          <t>239875; 296019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200831; 250282</t>
+          <t>199529; 248547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97950; 340386</t>
+          <t>114661; 337698</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>210453; 265884</t>
+          <t>210751; 262853</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>294141; 355829</t>
+          <t>294322; 357980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>296255; 357204</t>
+          <t>297148; 360695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>339022; 407220</t>
+          <t>337054; 404689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>117989; 156727</t>
+          <t>116040; 156715</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>208601; 259264</t>
+          <t>206922; 260558</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>231635; 287645</t>
+          <t>232060; 284159</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>133284; 328390</t>
+          <t>118993; 326914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>340100; 407432</t>
+          <t>340899; 408742</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514670; 601308</t>
+          <t>518594; 601865</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542204; 630808</t>
+          <t>544747; 630060</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>421350; 707722</t>
+          <t>437775; 710019</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>28360; 51770</t>
+          <t>27762; 51504</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111479; 151446</t>
+          <t>109488; 151498</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151664; 195998</t>
+          <t>152593; 195855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131005; 174769</t>
+          <t>133868; 173740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77307; 112094</t>
+          <t>77030; 113976</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>221647; 276992</t>
+          <t>222556; 273562</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>283410; 339147</t>
+          <t>281688; 337699</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>239691; 384846</t>
+          <t>257419; 390498</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111995; 154821</t>
+          <t>112271; 156009</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347403; 414302</t>
+          <t>345994; 415067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>446809; 522292</t>
+          <t>443735; 517273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>404796; 537966</t>
+          <t>394802; 538433</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10714; 28075</t>
+          <t>10137; 25884</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8965; 23918</t>
+          <t>8479; 23706</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19770; 41333</t>
+          <t>18921; 39795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27788; 62564</t>
+          <t>26669; 63102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>292952; 357503</t>
+          <t>297968; 360791</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>388375; 455042</t>
+          <t>389262; 454912</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>342803; 405249</t>
+          <t>341302; 405731</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>289659; 341173</t>
+          <t>290020; 341335</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>313629; 376907</t>
+          <t>314912; 379032</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>402339; 471833</t>
+          <t>401252; 470442</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>369218; 440437</t>
+          <t>367350; 441354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>326939; 389111</t>
+          <t>323408; 389168</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>504178; 587330</t>
+          <t>511424; 593110</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>808004; 917677</t>
+          <t>811307; 912489</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>876881; 980970</t>
+          <t>876675; 980787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>816632; 1179208</t>
+          <t>841527; 1181047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>648121; 742525</t>
+          <t>646001; 742347</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1123125; 1240312</t>
+          <t>1130354; 1242727</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1157198; 1276417</t>
+          <t>1154800; 1271970</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1004297; 1357447</t>
+          <t>1016340; 1353526</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1179381; 1312317</t>
+          <t>1179322; 1304734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1971456; 2126668</t>
+          <t>1970646; 2125479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2065070; 2229699</t>
+          <t>2056017; 2216051</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2018866; 2485436</t>
+          <t>2019848; 2490818</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P35-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P35-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,25; 21,49</t>
+          <t>14,52; 21,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 31,19</t>
+          <t>21,3; 31,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,76; 35,17</t>
+          <t>26,19; 35,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,83; 38,55</t>
+          <t>31,5; 40,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 21,26</t>
+          <t>12,26; 21,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,91; 33,4</t>
+          <t>23,34; 34,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,72; 34,45</t>
+          <t>24,39; 34,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,38</t>
+          <t>24,84; 31,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 19,87</t>
+          <t>14,64; 20,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,68; 30,77</t>
+          <t>23,54; 30,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,52; 33,4</t>
+          <t>26,73; 33,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,35; 34,01</t>
+          <t>29,59; 35,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,27</t>
+          <t>15,77; 24,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,39; 31,49</t>
+          <t>21,62; 31,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,61</t>
+          <t>23,53; 32,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,93; 43,08</t>
+          <t>34,04; 43,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 19,38</t>
+          <t>11,39; 19,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,01; 35,98</t>
+          <t>25,46; 36,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,97; 35,94</t>
+          <t>26,39; 36,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,07; 41,7</t>
+          <t>33,72; 41,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 20,09</t>
+          <t>14,5; 20,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 31,82</t>
+          <t>24,57; 31,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 32,86</t>
+          <t>26,17; 32,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,29; 41,54</t>
+          <t>35,47; 41,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 24,29</t>
+          <t>17,19; 24,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 32,83</t>
+          <t>25,25; 32,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 36,19</t>
+          <t>27,97; 35,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 40,35</t>
+          <t>34,23; 42,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 27,98</t>
+          <t>15,12; 28,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 42,27</t>
+          <t>30,51; 42,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,02; 44,44</t>
+          <t>28,64; 44,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,38; 48,02</t>
+          <t>35,07; 47,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 23,64</t>
+          <t>17,79; 24,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,8; 34,31</t>
+          <t>28,1; 34,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,44; 36,67</t>
+          <t>29,59; 37,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 40,43</t>
+          <t>35,56; 42,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 22,22</t>
+          <t>17,91; 22,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,8</t>
+          <t>25,92; 31,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,11; 31,69</t>
+          <t>25,99; 31,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,57; 39,11</t>
+          <t>33,2; 39,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 23,07</t>
+          <t>17,08; 23,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 35,09</t>
+          <t>28,33; 35,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 34,89</t>
+          <t>28,68; 35,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 33,48</t>
+          <t>30,11; 36,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 21,95</t>
+          <t>18,19; 21,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 32,21</t>
+          <t>27,63; 32,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,9; 32,27</t>
+          <t>28,02; 32,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 35,3</t>
+          <t>32,84; 36,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 15,49</t>
+          <t>7,89; 14,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,69; 30,02</t>
+          <t>21,85; 29,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,07; 32,17</t>
+          <t>24,98; 32,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,18; 36,57</t>
+          <t>26,37; 34,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 21,18</t>
+          <t>14,26; 21,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,12; 37,03</t>
+          <t>30,32; 37,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,46; 46,11</t>
+          <t>38,73; 45,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,68; 46,54</t>
+          <t>42,93; 48,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 17,92</t>
+          <t>12,65; 17,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,82; 33,38</t>
+          <t>28,17; 33,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,09; 38,57</t>
+          <t>33,28; 38,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 40,98</t>
+          <t>37,01; 41,96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,02</t>
+          <t>3,48; 9,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 9,33</t>
+          <t>3,53; 9,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,3</t>
+          <t>6,6; 13,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 26,24</t>
+          <t>14,65; 30,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 30,32</t>
+          <t>25,26; 30,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,24; 42,35</t>
+          <t>36,28; 42,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,12</t>
+          <t>31,98; 38,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,14; 44,89</t>
+          <t>38,94; 45,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,32; 25,66</t>
+          <t>21,16; 25,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,21; 35,41</t>
+          <t>30,2; 35,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,36; 32,88</t>
+          <t>27,56; 32,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,31; 38,88</t>
+          <t>34,42; 40,53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,0</t>
+          <t>16,23; 18,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,42; 27,46</t>
+          <t>24,39; 27,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,32; 29,45</t>
+          <t>26,25; 29,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,93; 34,98</t>
+          <t>33,12; 36,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,14; 23,15</t>
+          <t>20,2; 23,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,81; 36,07</t>
+          <t>32,56; 35,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,13; 36,5</t>
+          <t>33,2; 36,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,45; 37,89</t>
+          <t>36,91; 39,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 20,62</t>
+          <t>18,64; 20,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,12; 31,41</t>
+          <t>29,03; 31,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,16; 32,51</t>
+          <t>30,15; 32,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,07; 35,85</t>
+          <t>35,47; 37,74</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172798</t>
+          <t>196335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>138144</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>297344</t>
+          <t>334479</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64823; 97753</t>
+          <t>66052; 99924</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93943; 133323</t>
+          <t>91052; 133421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109100; 148937</t>
+          <t>110918; 150326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>150701; 194761</t>
+          <t>173455; 221406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37546; 62547</t>
+          <t>36084; 62999</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69734; 101646</t>
+          <t>71021; 104846</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85031; 118489</t>
+          <t>83890; 118723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>111115; 140402</t>
+          <t>121314; 155675</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108272; 148872</t>
+          <t>109685; 151026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173290; 225131</t>
+          <t>172251; 222117</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203538; 256355</t>
+          <t>205118; 259739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>270124; 324051</t>
+          <t>307457; 365898</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174339</t>
+          <t>189232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>142956</t>
+          <t>159028</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>317295</t>
+          <t>348260</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53594; 84424</t>
+          <t>54853; 84432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86333; 127088</t>
+          <t>87278; 125948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86598; 120230</t>
+          <t>86753; 121473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153453; 194822</t>
+          <t>164492; 208984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37674; 66553</t>
+          <t>39127; 65536</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82308; 118420</t>
+          <t>83806; 120347</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95063; 131531</t>
+          <t>96605; 132210</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>126255; 159179</t>
+          <t>142394; 175379</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99785; 138902</t>
+          <t>100258; 141435</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179205; 233150</t>
+          <t>180027; 231076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>188638; 241427</t>
+          <t>192268; 240094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>294288; 346434</t>
+          <t>321140; 379234</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164327</t>
+          <t>181742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69177</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>233504</t>
+          <t>259234</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88739; 125322</t>
+          <t>88712; 126839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152903; 199217</t>
+          <t>153229; 199904</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141552; 185900</t>
+          <t>143655; 184883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61303; 269612</t>
+          <t>161425; 202455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24194; 45267</t>
+          <t>24456; 46627</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76836; 108199</t>
+          <t>78108; 108767</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47623; 72933</t>
+          <t>47010; 72239</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59050; 80147</t>
+          <t>65763; 89848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>119667; 160178</t>
+          <t>120544; 163984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>239875; 296019</t>
+          <t>242436; 298561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199529; 248547</t>
+          <t>200579; 251098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>114661; 337698</t>
+          <t>234400; 280466</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371135</t>
+          <t>410101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>252707</t>
+          <t>282508</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>623842</t>
+          <t>692610</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>210751; 262853</t>
+          <t>211880; 264518</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>294322; 357980</t>
+          <t>291758; 357102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>297148; 360695</t>
+          <t>295786; 358249</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>337054; 404689</t>
+          <t>375805; 445768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>116040; 156715</t>
+          <t>116005; 157929</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>206922; 260558</t>
+          <t>210332; 262241</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>232060; 284159</t>
+          <t>233586; 286112</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>118993; 326914</t>
+          <t>258877; 310734</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>340899; 408742</t>
+          <t>338766; 405816</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>518594; 601865</t>
+          <t>516197; 601927</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>544747; 630060</t>
+          <t>547009; 626984</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>437775; 710019</t>
+          <t>654072; 736749</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152589</t>
+          <t>171253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>339448</t>
+          <t>378461</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>492037</t>
+          <t>549714</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27762; 51504</t>
+          <t>26232; 49432</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109488; 151498</t>
+          <t>110285; 150839</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152593; 195855</t>
+          <t>152054; 197148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133868; 173740</t>
+          <t>149766; 198753</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77030; 113976</t>
+          <t>76750; 113250</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>222556; 273562</t>
+          <t>223995; 275300</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>281688; 337699</t>
+          <t>283626; 335754</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>257419; 390498</t>
+          <t>356363; 403064</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112271; 156009</t>
+          <t>110131; 153453</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345994; 415067</t>
+          <t>350339; 412902</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>443735; 517273</t>
+          <t>446343; 516969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>394802; 538433</t>
+          <t>517498; 586610</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>315571</t>
+          <t>353892</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>358105</t>
+          <t>404569</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10137; 25884</t>
+          <t>9993; 25831</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8479; 23706</t>
+          <t>8981; 23683</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18921; 39795</t>
+          <t>18357; 38457</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26669; 63102</t>
+          <t>34749; 73399</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>297968; 360791</t>
+          <t>300568; 360883</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>389262; 454912</t>
+          <t>389681; 456990</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>341302; 405731</t>
+          <t>340327; 406490</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>290020; 341335</t>
+          <t>328400; 383777</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>314912; 379032</t>
+          <t>312519; 376370</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>401252; 470442</t>
+          <t>401237; 473918</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>367350; 441354</t>
+          <t>369986; 436400</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>323408; 389168</t>
+          <t>371874; 437929</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1077723</t>
+          <t>1199340</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1244405</t>
+          <t>1389526</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2322128</t>
+          <t>2588866</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>511424; 593110</t>
+          <t>506361; 590009</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>811307; 912489</t>
+          <t>810276; 915555</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>876675; 980787</t>
+          <t>874362; 980659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>841527; 1181047</t>
+          <t>1140000; 1258432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>646001; 742347</t>
+          <t>647800; 741561</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1130354; 1242727</t>
+          <t>1121727; 1237921</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1154800; 1271970</t>
+          <t>1157119; 1270144</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1016340; 1353526</t>
+          <t>1340316; 1443553</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1179322; 1304734</t>
+          <t>1179402; 1302498</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1970646; 2125479</t>
+          <t>1964633; 2127692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2056017; 2216051</t>
+          <t>2055139; 2215215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2019848; 2490818</t>
+          <t>2509362; 2669692</t>
         </is>
       </c>
     </row>
